--- a/data/trans_bre/P19C03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C03-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 14,29</t>
+          <t>-4,75; 15,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 15,45</t>
+          <t>-0,08; 14,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 2,85</t>
+          <t>-13,82; 2,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 15,03</t>
+          <t>2,27; 14,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 44,34</t>
+          <t>-12,3; 51,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 103,62</t>
+          <t>-0,31; 98,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 12,3</t>
+          <t>-43,12; 10,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,22; 131,97</t>
+          <t>10,24; 126,12</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 3,69</t>
+          <t>-8,61; 3,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 7,08</t>
+          <t>-6,44; 6,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 0,63</t>
+          <t>-12,55; 0,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 0,58</t>
+          <t>-12,78; 0,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 12,66</t>
+          <t>-23,57; 11,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 26,27</t>
+          <t>-18,72; 25,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,8; 2,68</t>
+          <t>-35,49; 2,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 2,63</t>
+          <t>-39,46; 2,81</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 6,37</t>
+          <t>-9,67; 6,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 1,05</t>
+          <t>-13,59; 0,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 3,38</t>
+          <t>-10,21; 4,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 1,44</t>
+          <t>-8,99; 1,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 23,97</t>
+          <t>-25,94; 24,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,02; 3,39</t>
+          <t>-37,19; 3,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 13,55</t>
+          <t>-33,22; 17,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-44,64; 9,76</t>
+          <t>-41,17; 14,83</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 7,9</t>
+          <t>-6,76; 8,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,19; -1,97</t>
+          <t>-15,78; -1,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 12,43</t>
+          <t>0,07; 13,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 20,1</t>
+          <t>-8,67; 20,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 30,73</t>
+          <t>-19,59; 30,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,13; -5,45</t>
+          <t>-41,63; -5,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 84,87</t>
+          <t>0,41; 89,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,72; 125,3</t>
+          <t>-40,26; 136,87</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 9,38</t>
+          <t>-10,58; 9,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 7,68</t>
+          <t>-11,08; 7,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 9,96</t>
+          <t>-9,96; 10,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 8,28</t>
+          <t>-4,61; 7,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,24; 41,89</t>
+          <t>-31,67; 38,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,27; 28,71</t>
+          <t>-30,64; 31,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 54,0</t>
+          <t>-33,29; 63,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 46,93</t>
+          <t>-18,86; 46,91</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 5,73</t>
+          <t>-11,55; 5,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 8,85</t>
+          <t>-8,15; 8,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 6,24</t>
+          <t>-8,25; 6,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,5; -1,09</t>
+          <t>-13,73; -0,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 23,16</t>
+          <t>-34,7; 23,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 39,78</t>
+          <t>-26,27; 36,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 32,89</t>
+          <t>-30,55; 38,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,22; -4,2</t>
+          <t>-50,11; -4,04</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 3,66</t>
+          <t>-8,29; 3,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 3,04</t>
+          <t>-7,93; 2,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 4,04</t>
+          <t>-9,29; 4,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,76; -0,82</t>
+          <t>-18,07; -1,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 12,22</t>
+          <t>-22,39; 12,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 11,31</t>
+          <t>-24,24; 10,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 12,01</t>
+          <t>-24,04; 12,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-67,97; -3,61</t>
+          <t>-69,75; -4,77</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 10,24</t>
+          <t>-1,32; 10,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 6,95</t>
+          <t>-3,84; 6,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 5,79</t>
+          <t>-4,24; 6,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 9,58</t>
+          <t>0,7; 10,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 37,91</t>
+          <t>-3,9; 36,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 24,28</t>
+          <t>-11,15; 23,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 24,1</t>
+          <t>-14,66; 26,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 249,46</t>
+          <t>5,62; 299,34</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,75</t>
+          <t>-2,58; 2,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,21</t>
+          <t>-3,5; 1,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,14</t>
+          <t>-3,57; 1,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,76</t>
+          <t>-3,8; 4,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 9,06</t>
+          <t>-7,8; 9,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 4,17</t>
+          <t>-11,21; 5,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 4,17</t>
+          <t>-12,49; 4,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 24,24</t>
+          <t>-19,68; 25,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C03-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C03-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,07</t>
+          <t>7,19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 15,48</t>
+          <t>-5,27; 14,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 14,97</t>
+          <t>0,08; 15,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 2,25</t>
+          <t>-13,16; 2,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 14,35</t>
+          <t>0,89; 13,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 51,9</t>
+          <t>-13,53; 46,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 98,35</t>
+          <t>0,12; 101,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,12; 10,04</t>
+          <t>-40,93; 11,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 126,12</t>
+          <t>4,5; 97,08</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,63</t>
+          <t>-4,79</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-20,45%</t>
+          <t>-17,72%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 3,31</t>
+          <t>-9,9; 3,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 6,87</t>
+          <t>-5,4; 7,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 0,58</t>
+          <t>-13,16; 0,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 0,57</t>
+          <t>-10,6; 1,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 11,42</t>
+          <t>-25,85; 11,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 25,07</t>
+          <t>-16,22; 26,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,49; 2,1</t>
+          <t>-36,76; 2,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 2,81</t>
+          <t>-35,31; 7,02</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,7</t>
+          <t>-3,71</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-20,61%</t>
+          <t>-20,42%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 6,29</t>
+          <t>-10,1; 6,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 0,88</t>
+          <t>-13,47; 1,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 4,07</t>
+          <t>-11,0; 2,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 1,89</t>
+          <t>-8,95; 1,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 24,4</t>
+          <t>-28,52; 25,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 3,03</t>
+          <t>-36,71; 4,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 17,73</t>
+          <t>-33,98; 12,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 14,83</t>
+          <t>-41,06; 10,77</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>-2,29%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 8,12</t>
+          <t>-7,37; 8,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,78; -1,66</t>
+          <t>-16,35; -1,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 13,14</t>
+          <t>-0,51; 13,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 20,13</t>
+          <t>-8,49; 6,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 30,28</t>
+          <t>-20,69; 30,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,63; -5,2</t>
+          <t>-43,28; -4,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 89,84</t>
+          <t>-2,56; 88,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 136,87</t>
+          <t>-33,68; 43,58</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 9,3</t>
+          <t>-11,39; 8,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 7,98</t>
+          <t>-10,76; 9,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 10,58</t>
+          <t>-12,33; 9,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 7,95</t>
+          <t>-5,18; 7,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,67; 38,22</t>
+          <t>-33,66; 37,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 31,45</t>
+          <t>-28,75; 33,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 63,03</t>
+          <t>-38,99; 51,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 46,91</t>
+          <t>-21,38; 41,78</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-6,96</t>
+          <t>-7,38</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-30,12%</t>
+          <t>-31,41%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 5,58</t>
+          <t>-11,84; 6,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 8,02</t>
+          <t>-7,68; 8,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 6,83</t>
+          <t>-8,71; 6,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,73; -0,8</t>
+          <t>-13,71; -1,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,7; 23,34</t>
+          <t>-35,56; 28,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 36,19</t>
+          <t>-25,6; 39,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 38,03</t>
+          <t>-32,07; 35,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,11; -4,04</t>
+          <t>-50,42; -7,86</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-7,73</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-33,19%</t>
+          <t>-5,38%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 3,85</t>
+          <t>-8,42; 4,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 2,94</t>
+          <t>-7,85; 2,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 4,03</t>
+          <t>-9,01; 3,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,07; -1,09</t>
+          <t>-5,35; 3,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 12,91</t>
+          <t>-22,86; 13,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 10,85</t>
+          <t>-23,54; 10,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-24,04; 12,43</t>
+          <t>-22,82; 10,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-69,75; -4,77</t>
+          <t>-22,07; 18,32</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 10,3</t>
+          <t>-1,1; 9,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 6,9</t>
+          <t>-3,66; 6,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 6,41</t>
+          <t>-3,8; 5,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 10,44</t>
+          <t>-1,31; 4,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 36,92</t>
+          <t>-3,31; 35,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 23,38</t>
+          <t>-10,59; 23,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 26,89</t>
+          <t>-13,32; 25,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,62; 299,34</t>
+          <t>-11,54; 53,33</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-2,79%</t>
+          <t>-4,16%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,75</t>
+          <t>-2,38; 2,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,52</t>
+          <t>-3,67; 1,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,15</t>
+          <t>-3,68; 0,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 4,09</t>
+          <t>-2,78; 1,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 9,03</t>
+          <t>-7,27; 9,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 5,28</t>
+          <t>-11,64; 4,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 4,33</t>
+          <t>-12,85; 3,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 25,83</t>
+          <t>-13,84; 5,73</t>
         </is>
       </c>
     </row>
